--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2758-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2758-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{836D1941-DB85-46CD-986F-6209A3DEF145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC456C5A-D266-4BB1-A7A3-84DB079FC996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C3F0BD25-7938-4D14-B5AC-574A1B1D25C4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C123AC07-05DF-433A-8645-94ED244AF7CD}"/>
   </bookViews>
   <sheets>
     <sheet name="2758-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1507,21 +1507,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F836FBB4-AE35-4A2D-B9EF-2E086DECA88F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7919598-BEA4-46DC-B315-43C066EF3AF5}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1711,7 +1711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1819,7 +1819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2022</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2021</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2020</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>30</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
         <v>42</v>
       </c>
